--- a/Quan Trac Lun/Templates/Template 03.xlsx
+++ b/Quan Trac Lun/Templates/Template 03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71DAE0E5-BCE9-48E2-807A-1B34A169CF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5857391A-2B53-41E8-907B-EA17425E54C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="30">
   <si>
     <t>BIỂU GHI ĐO QUAN TRẮC LÚN</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Phải</t>
-  </si>
-  <si>
-    <t>chân ta luy phải</t>
   </si>
   <si>
     <t>Nhà thầu</t>
@@ -135,9 +132,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-1010000]d/m/yyyy;@"/>
-  </numFmts>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -147,11 +141,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
@@ -160,17 +172,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
@@ -178,22 +180,20 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="MS Sans Serif"/>
-      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -210,7 +210,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -467,137 +467,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,14 +949,15 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.69921875" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.69921875" style="46" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16.8">
+    <row r="1" spans="1:28" ht="32.4" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -972,450 +985,436 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="3"/>
+      <c r="AB1" s="3"/>
     </row>
-    <row r="2" spans="1:29" ht="16.8">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="6"/>
+    <row r="2" spans="1:28" ht="16.8">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="7"/>
     </row>
-    <row r="3" spans="1:29" ht="16.8">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="6"/>
+    <row r="3" spans="1:28" ht="16.8">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="7"/>
     </row>
-    <row r="4" spans="1:29" ht="16.8">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:28" ht="16.8">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="10"/>
     </row>
-    <row r="5" spans="1:29">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:28">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
       <c r="M5" s="13"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12" t="s">
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="14"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="15"/>
     </row>
-    <row r="6" spans="1:29">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:28">
+      <c r="A6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
       <c r="M6" s="18"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17" t="s">
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="17"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="19"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="18"/>
+      <c r="AA6" s="18"/>
+      <c r="AB6" s="22"/>
     </row>
-    <row r="7" spans="1:29">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:28">
+      <c r="A7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22" t="s">
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="T7" s="22"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="24"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="28"/>
     </row>
-    <row r="8" spans="1:29" ht="13.8" customHeight="1">
-      <c r="A8" s="41" t="s">
+    <row r="8" spans="1:28" ht="13.8" customHeight="1">
+      <c r="A8" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="27" t="s">
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="27" t="s">
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="27" t="s">
+      <c r="M8" s="33"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="31" t="s">
+      <c r="P8" s="33"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="T8" s="32"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="31" t="s">
+      <c r="S8" s="36"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="W8" s="32"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="25" t="s">
+      <c r="V8" s="36"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="Z8" s="25" t="s">
+      <c r="Y8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="AA8" s="25" t="s">
+      <c r="Z8" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="AB8" s="31" t="s">
+      <c r="AA8" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AC8" s="33"/>
+      <c r="AB8" s="37"/>
     </row>
-    <row r="9" spans="1:29" ht="27.6">
-      <c r="A9" s="42"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="35" t="s">
+    <row r="9" spans="1:28">
+      <c r="A9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="35" t="s">
+      <c r="L9" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="S9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="V9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="W9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="T9" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="U9" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="V9" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="W9" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="X9" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="35" t="s">
+      <c r="AB9" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="AC9" s="36" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="10" spans="1:29">
-      <c r="A10" s="43"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="37" t="s">
+    <row r="10" spans="1:28">
+      <c r="A10" s="40"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="S10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="T10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="U10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="V10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="W10" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="T10" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="U10" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="V10" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="W10" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="X10" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="39"/>
+      <c r="X10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="44"/>
+      <c r="AB10" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AB8:AC8"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
     <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="A3:AB3"/>
+    <mergeCell ref="A4:AB4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A2:AC2"/>
-    <mergeCell ref="A3:AC3"/>
-    <mergeCell ref="A4:AC4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="AA8:AB8"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Quan Trac Lun/Templates/Template 03.xlsx
+++ b/Quan Trac Lun/Templates/Template 03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5857391A-2B53-41E8-907B-EA17425E54C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9417568B-8648-4861-A421-B08C2BD77674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
   <si>
     <t>BIỂU GHI ĐO QUAN TRẮC LÚN</t>
   </si>
@@ -125,7 +125,10 @@
     <t>( mm)</t>
   </si>
   <si>
-    <t>Ngày Quan trắc</t>
+    <t xml:space="preserve">Ngày </t>
+  </si>
+  <si>
+    <t>Quan trắc</t>
   </si>
 </sst>
 </file>
@@ -492,51 +495,12 @@
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -546,70 +510,107 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -952,453 +953,449 @@
   <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.69921875" style="46" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="4"/>
+    <col min="1" max="1" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.69921875" style="20" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="32.4" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="3"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="30"/>
     </row>
     <row r="2" spans="1:28" ht="16.8">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="7"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="33"/>
     </row>
     <row r="3" spans="1:28" ht="16.8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="7"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="33"/>
     </row>
     <row r="4" spans="1:28" ht="16.8">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="10"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="36"/>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="15"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="S6" s="20"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="22"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25" t="s">
+      <c r="C7" s="42"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="S7" s="25"/>
-      <c r="T7" s="27"/>
-      <c r="U7" s="25"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="25"/>
-      <c r="X7" s="25"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="25"/>
-      <c r="AA7" s="25"/>
-      <c r="AB7" s="28"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="13"/>
     </row>
     <row r="8" spans="1:28" ht="13.8" customHeight="1">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="32" t="s">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="32" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="32" t="s">
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="35" t="s">
+      <c r="P8" s="23"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="36"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="35" t="s">
+      <c r="S8" s="26"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="36"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="31" t="s">
+      <c r="V8" s="26"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="Y8" s="31" t="s">
+      <c r="Y8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="31" t="s">
+      <c r="Z8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="35" t="s">
+      <c r="AA8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AB8" s="37"/>
+      <c r="AB8" s="27"/>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="41" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="41" t="s">
+      <c r="M9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="41" t="s">
+      <c r="N9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="41" t="s">
+      <c r="P9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="41" t="s">
+      <c r="Q9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="41" t="s">
+      <c r="R9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="41" t="s">
+      <c r="S9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="T9" s="41" t="s">
+      <c r="T9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="41" t="s">
+      <c r="U9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="V9" s="41" t="s">
+      <c r="V9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="W9" s="41" t="s">
+      <c r="W9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="41" t="s">
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="AB9" s="42" t="s">
+      <c r="AB9" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:28">
-      <c r="A10" s="40"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="44" t="s">
+      <c r="A10" s="45"/>
+      <c r="B10" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="S10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="T10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="U10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="V10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="W10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="X10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="45"/>
+      <c r="X10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="18"/>
+      <c r="AB10" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
+  <mergeCells count="21">
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:K8"/>
@@ -1411,10 +1408,15 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Quan Trac Lun/Templates/Template 03.xlsx
+++ b/Quan Trac Lun/Templates/Template 03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9417568B-8648-4861-A421-B08C2BD77674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5790B89-8FE1-417F-A984-7741471D36A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
+    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -157,14 +157,14 @@
       <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -173,7 +173,7 @@
       <u/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -181,20 +181,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -535,6 +535,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -545,15 +546,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -610,7 +602,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -951,141 +951,141 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.69921875" style="20" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="20" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.4" customHeight="1">
-      <c r="A1" s="28"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="30"/>
+    <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
+      <c r="A1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="28"/>
     </row>
-    <row r="2" spans="1:28" ht="16.8">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="33"/>
+    <row r="2" spans="1:28" ht="17.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="31"/>
     </row>
-    <row r="3" spans="1:28" ht="16.8">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="33"/>
+    <row r="3" spans="1:28" ht="17.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="31"/>
     </row>
-    <row r="4" spans="1:28" ht="16.8">
-      <c r="A4" s="34" t="s">
+    <row r="4" spans="1:28" ht="17.25">
+      <c r="A4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="36"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="34"/>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1115,11 +1115,11 @@
       <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1149,13 +1149,13 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1184,72 +1184,72 @@
       <c r="AA7" s="10"/>
       <c r="AB7" s="13"/>
     </row>
-    <row r="8" spans="1:28" ht="13.8" customHeight="1">
-      <c r="A8" s="43" t="s">
+    <row r="8" spans="1:28" ht="13.9" customHeight="1">
+      <c r="A8" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="43" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="22" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="22" t="s">
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="22" t="s">
+      <c r="M8" s="24"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="25" t="s">
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="25" t="s">
+      <c r="S8" s="46"/>
+      <c r="T8" s="45"/>
+      <c r="U8" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="26"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="21" t="s">
+      <c r="V8" s="46"/>
+      <c r="W8" s="45"/>
+      <c r="X8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="Y8" s="21" t="s">
+      <c r="Y8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="21" t="s">
+      <c r="Z8" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="25" t="s">
+      <c r="AA8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="AB8" s="27"/>
+      <c r="AB8" s="45"/>
     </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="44"/>
+    <row r="9" spans="1:28" ht="30">
+      <c r="A9" s="42"/>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="21"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1304,9 +1304,9 @@
       <c r="W9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
       <c r="AA9" s="14" t="s">
         <v>25</v>
       </c>
@@ -1314,8 +1314,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="45"/>
+    <row r="10" spans="1:28" ht="30">
+      <c r="A10" s="43"/>
       <c r="B10" s="17" t="s">
         <v>30</v>
       </c>
@@ -1396,6 +1396,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:K8"/>
@@ -1412,11 +1417,6 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Quan Trac Lun/Templates/Template 03.xlsx
+++ b/Quan Trac Lun/Templates/Template 03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5790B89-8FE1-417F-A984-7741471D36A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F43994-65A4-4F5A-9CEA-F6E6FBB535ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -157,14 +157,14 @@
       <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -173,7 +173,7 @@
       <u/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -181,20 +181,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -536,16 +536,25 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -600,15 +609,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -951,141 +951,141 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="20" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.69921875" style="20" customWidth="1"/>
+    <col min="3" max="16384" width="8.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="26"/>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="28"/>
+    <row r="1" spans="1:28" ht="32.4" customHeight="1">
+      <c r="A1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="31"/>
     </row>
-    <row r="2" spans="1:28" ht="17.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="31"/>
+    <row r="2" spans="1:28" ht="16.8">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="34"/>
     </row>
-    <row r="3" spans="1:28" ht="17.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="31"/>
+    <row r="3" spans="1:28" ht="16.8">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="33"/>
+      <c r="AB3" s="34"/>
     </row>
-    <row r="4" spans="1:28" ht="17.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:28" ht="16.8">
+      <c r="A4" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="34"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="37"/>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1115,11 +1115,11 @@
       <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1149,13 +1149,13 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1184,72 +1184,72 @@
       <c r="AA7" s="10"/>
       <c r="AB7" s="13"/>
     </row>
-    <row r="8" spans="1:28" ht="13.9" customHeight="1">
-      <c r="A8" s="41" t="s">
+    <row r="8" spans="1:28" ht="13.95" customHeight="1">
+      <c r="A8" s="44" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="21"/>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="23" t="s">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="23" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="24"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="23" t="s">
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="44" t="s">
+      <c r="P8" s="23"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="46"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="44" t="s">
+      <c r="S8" s="26"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="46"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="22" t="s">
+      <c r="V8" s="26"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="Y8" s="22" t="s">
+      <c r="Y8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="22" t="s">
+      <c r="Z8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="44" t="s">
+      <c r="AA8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AB8" s="45"/>
+      <c r="AB8" s="27"/>
     </row>
-    <row r="9" spans="1:28" ht="30">
-      <c r="A9" s="42"/>
+    <row r="9" spans="1:28">
+      <c r="A9" s="45"/>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="22"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1304,9 +1304,9 @@
       <c r="W9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
       <c r="AA9" s="14" t="s">
         <v>25</v>
       </c>
@@ -1314,55 +1314,55 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="30">
-      <c r="A10" s="43"/>
+    <row r="10" spans="1:28">
+      <c r="A10" s="46"/>
       <c r="B10" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R10" s="18" t="s">
         <v>28</v>
@@ -1396,11 +1396,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:K8"/>
@@ -1417,6 +1412,11 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
